--- a/br-addexamples-PSindiv/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
+++ b/br-addexamples-PSindiv/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T09:43:13+00:00</t>
+    <t>2024-07-17T11:59:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/br-addexamples-PSindiv/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
+++ b/br-addexamples-PSindiv/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T11:59:52+00:00</t>
+    <t>2024-07-18T08:12:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/br-addexamples-PSindiv/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
+++ b/br-addexamples-PSindiv/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-18T08:12:53+00:00</t>
+    <t>2024-07-18T08:45:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/br-addexamples-PSindiv/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
+++ b/br-addexamples-PSindiv/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-18T08:45:44+00:00</t>
+    <t>2024-07-18T12:33:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/br-addexamples-PSindiv/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
+++ b/br-addexamples-PSindiv/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-18T12:33:27+00:00</t>
+    <t>2024-07-18T12:48:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/br-addexamples-PSindiv/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
+++ b/br-addexamples-PSindiv/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-18T12:48:07+00:00</t>
+    <t>2024-07-19T07:50:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/br-addexamples-PSindiv/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
+++ b/br-addexamples-PSindiv/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-19T07:50:01+00:00</t>
+    <t>2024-07-19T11:24:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/br-addexamples-PSindiv/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
+++ b/br-addexamples-PSindiv/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-19T11:24:32+00:00</t>
+    <t>2024-07-19T11:42:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/br-addexamples-PSindiv/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
+++ b/br-addexamples-PSindiv/ig/StructureDefinition-sas-cpts-organization-aggregator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-19T11:42:31+00:00</t>
+    <t>2024-07-19T11:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
